--- a/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - November-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (Deffodils)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CB67C9-4EA5-48AE-A036-2DCCEA0AE98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C0F447-25F9-4293-8B2C-F754F827C823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (Daffodil) (Girls)" sheetId="17" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="137">
   <si>
     <t>S.No</t>
   </si>
@@ -388,9 +388,6 @@
     <t>Ab. Hadi</t>
   </si>
   <si>
-    <t>Monthly Attendence Month of October-2024</t>
-  </si>
-  <si>
     <t>SUNDAY - SUNDAY - SUNDAY</t>
   </si>
   <si>
@@ -443,6 +440,12 @@
   </si>
   <si>
     <t>IQBAL DAY - IQBAL DAY</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of November-2024</t>
   </si>
 </sst>
 </file>
@@ -722,8 +725,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -733,6 +739,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -746,11 +755,14 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
@@ -761,36 +773,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -835,16 +845,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -866,14 +866,24 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -884,13 +894,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -974,54 +977,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1032,57 +990,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1408,43 +1315,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
       <c r="AJ1" s="16"/>
       <c r="AK1" s="16"/>
       <c r="AL1" s="16"/>
@@ -1453,43 +1360,43 @@
       <c r="AO1" s="16"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
+      <c r="A2" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
       <c r="AJ2" s="16"/>
       <c r="AK2" s="16"/>
       <c r="AL2" s="16"/>
@@ -1498,19 +1405,19 @@
       <c r="AO2" s="16"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1633,25 +1540,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="29"/>
+      <c r="AM3" s="34"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="13">
         <v>45597</v>
       </c>
@@ -1742,8 +1649,8 @@
       <c r="AI4" s="13">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
+      <c r="AJ4" s="37"/>
+      <c r="AK4" s="37"/>
       <c r="AL4" s="3" t="s">
         <v>7</v>
       </c>
@@ -1770,71 +1677,77 @@
         <v>8</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>118</v>
+        <v>118</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N5" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>118</v>
+        <v>118</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="30" t="s">
-        <v>118</v>
+        <v>118</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
-      <c r="Y5" s="49"/>
+      <c r="Y5" s="30"/>
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
-      <c r="AC5" s="30" t="s">
-        <v>118</v>
+      <c r="AC5" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
-      <c r="AF5" s="49"/>
+      <c r="AF5" s="30"/>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="4">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>10</v>
+        <f t="shared" ref="AJ5:AJ29" si="1">COUNTIF(F5:AI5,"P")</f>
+        <v>13</v>
       </c>
       <c r="AK5" s="4">
-        <f>COUNTIF(F5:AI5,"A")</f>
+        <f t="shared" ref="AK5:AK29" si="2">COUNTIF(F5:AI5,"A")</f>
         <v>0</v>
       </c>
       <c r="AL5" s="4" t="s">
@@ -1865,61 +1778,67 @@
         <v>8</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H6" s="32"/>
       <c r="I6" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N6" s="40"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="31"/>
+        <v>135</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="V6" s="32"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
-      <c r="Y6" s="49"/>
+      <c r="Y6" s="30"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
-      <c r="AC6" s="31"/>
+      <c r="AC6" s="32"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
-      <c r="AF6" s="49"/>
+      <c r="AF6" s="30"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="4">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="AK6" s="4">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL6" s="4" t="s">
@@ -1948,61 +1867,67 @@
         <v>8</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H7" s="32"/>
       <c r="I7" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N7" s="40"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V7" s="32"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
-      <c r="Y7" s="49"/>
+      <c r="Y7" s="30"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
-      <c r="AC7" s="31"/>
+      <c r="AC7" s="32"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
-      <c r="AF7" s="49"/>
+      <c r="AF7" s="30"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="4">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK7" s="4">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL7" s="17"/>
@@ -2027,69 +1952,73 @@
         <v>8</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H8" s="32"/>
       <c r="I8" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="N8" s="40"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="31"/>
+      <c r="T8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V8" s="32"/>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
-      <c r="Y8" s="49"/>
+      <c r="Y8" s="30"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="31"/>
+      <c r="AC8" s="32"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
-      <c r="AF8" s="49"/>
+      <c r="AF8" s="30"/>
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8"/>
       <c r="AJ8" s="4">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK8" s="4">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL8" s="29" t="s">
+      <c r="AL8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="34"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -2108,61 +2037,65 @@
         <v>8</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="H9" s="32"/>
       <c r="I9" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9" s="47"/>
-      <c r="O9" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N9" s="40"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="31"/>
+      <c r="T9" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V9" s="32"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
-      <c r="Y9" s="49"/>
+      <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-      <c r="AC9" s="31"/>
+      <c r="AC9" s="32"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
-      <c r="AF9" s="49"/>
+      <c r="AF9" s="30"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="4">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK9" s="4">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL9" s="4" t="s">
@@ -2195,61 +2128,65 @@
         <v>8</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H10" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H10" s="32"/>
       <c r="I10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N10" s="47"/>
-      <c r="O10" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N10" s="40"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="31"/>
+      <c r="T10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V10" s="32"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
-      <c r="Y10" s="49"/>
+      <c r="Y10" s="30"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-      <c r="AC10" s="31"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
-      <c r="AF10" s="49"/>
+      <c r="AF10" s="30"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="8"/>
       <c r="AJ10" s="4">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK10" s="4">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL10" s="4" t="s">
@@ -2285,61 +2222,65 @@
         <v>8</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H11" s="32"/>
       <c r="I11" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N11" s="47"/>
-      <c r="O11" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N11" s="40"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="31"/>
+      <c r="T11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V11" s="32"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
-      <c r="Y11" s="49"/>
+      <c r="Y11" s="30"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-      <c r="AC11" s="31"/>
+      <c r="AC11" s="32"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
-      <c r="AF11" s="49"/>
+      <c r="AF11" s="30"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="4">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK11" s="4">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL11" s="4" t="s">
@@ -2347,15 +2288,15 @@
       </c>
       <c r="AM11" s="9">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28</f>
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AN11" s="9">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AO11" s="9">
         <f>AM11+AN11</f>
-        <v>215</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2375,61 +2316,65 @@
         <v>8</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="H12" s="32"/>
       <c r="I12" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N12" s="40"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="31"/>
+      <c r="T12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V12" s="32"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
-      <c r="Y12" s="49"/>
+      <c r="Y12" s="30"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-      <c r="AC12" s="31"/>
+      <c r="AC12" s="32"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
-      <c r="AF12" s="49"/>
+      <c r="AF12" s="30"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="4">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK12" s="4">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL12" s="4" t="s">
@@ -2437,15 +2382,15 @@
       </c>
       <c r="AM12" s="9">
         <f>AM11/AM10</f>
-        <v>0.2874493927125506</v>
+        <v>0.34008097165991902</v>
       </c>
       <c r="AN12" s="9">
         <f>AN11/AN10</f>
-        <v>0.1336996336996337</v>
+        <v>0.1575091575091575</v>
       </c>
       <c r="AO12" s="9">
         <f>AO11/AO10</f>
-        <v>0.20673076923076922</v>
+        <v>0.24423076923076922</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2465,61 +2410,65 @@
         <v>8</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H13" s="32"/>
       <c r="I13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N13" s="47"/>
-      <c r="O13" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N13" s="40"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="31"/>
+      <c r="T13" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V13" s="32"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
-      <c r="Y13" s="49"/>
+      <c r="Y13" s="30"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-      <c r="AC13" s="31"/>
+      <c r="AC13" s="32"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
-      <c r="AF13" s="49"/>
+      <c r="AF13" s="30"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="4">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK13" s="4">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL13" s="17"/>
@@ -2544,61 +2493,65 @@
         <v>8</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H14" s="32"/>
       <c r="I14" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N14" s="47"/>
-      <c r="O14" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N14" s="40"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="31"/>
+      <c r="T14" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="V14" s="32"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Y14" s="49"/>
+      <c r="Y14" s="30"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-      <c r="AC14" s="31"/>
+      <c r="AC14" s="32"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
-      <c r="AF14" s="49"/>
+      <c r="AF14" s="30"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
       <c r="AJ14" s="4">
-        <f>COUNTIF(F14:AI14,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AK14" s="4">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL14" s="20"/>
@@ -2623,61 +2576,65 @@
         <v>8</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N15" s="47"/>
-      <c r="O15" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N15" s="40"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="31"/>
+      <c r="T15" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V15" s="32"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
-      <c r="Y15" s="49"/>
+      <c r="Y15" s="30"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-      <c r="AC15" s="31"/>
+      <c r="AC15" s="32"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
-      <c r="AF15" s="49"/>
+      <c r="AF15" s="30"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="4">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK15" s="4">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL15" s="17"/>
@@ -2702,69 +2659,73 @@
         <v>8</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H16" s="32"/>
       <c r="I16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N16" s="47"/>
-      <c r="O16" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N16" s="40"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="31"/>
+      <c r="T16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V16" s="32"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
-      <c r="Y16" s="49"/>
+      <c r="Y16" s="30"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-      <c r="AC16" s="31"/>
+      <c r="AC16" s="32"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
-      <c r="AF16" s="49"/>
+      <c r="AF16" s="30"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="4">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK16" s="4">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="29" t="s">
+      <c r="AL16" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="29"/>
+      <c r="AM16" s="34"/>
+      <c r="AN16" s="34"/>
+      <c r="AO16" s="34"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -2783,61 +2744,65 @@
         <v>8</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="H17" s="32"/>
       <c r="I17" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N17" s="47"/>
-      <c r="O17" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N17" s="40"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="31"/>
+      <c r="T17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V17" s="32"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
-      <c r="Y17" s="49"/>
+      <c r="Y17" s="30"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-      <c r="AC17" s="31"/>
+      <c r="AC17" s="32"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
-      <c r="AF17" s="49"/>
+      <c r="AF17" s="30"/>
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
       <c r="AJ17" s="4">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK17" s="4">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL17" s="4" t="s">
@@ -2870,61 +2835,65 @@
         <v>8</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H18" s="32"/>
       <c r="I18" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N18" s="47"/>
-      <c r="O18" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N18" s="40"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="31"/>
+      <c r="T18" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="V18" s="32"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
-      <c r="Y18" s="49"/>
+      <c r="Y18" s="30"/>
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AC18" s="31"/>
+      <c r="AC18" s="32"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
-      <c r="AF18" s="49"/>
+      <c r="AF18" s="30"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="4">
-        <f>COUNTIF(F18:AI18,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AK18" s="4">
-        <f>COUNTIF(F18:AI18,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL18" s="4" t="s">
@@ -2960,61 +2929,65 @@
         <v>8</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H19" s="32"/>
       <c r="I19" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N19" s="47"/>
-      <c r="O19" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N19" s="40"/>
+      <c r="O19" s="32"/>
       <c r="P19" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="31"/>
+      <c r="T19" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="V19" s="32"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
-      <c r="Y19" s="49"/>
+      <c r="Y19" s="30"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="31"/>
+      <c r="AC19" s="32"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
-      <c r="AF19" s="49"/>
+      <c r="AF19" s="30"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
       <c r="AJ19" s="4">
-        <f>COUNTIF(F19:AI19,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AK19" s="4">
-        <f>COUNTIF(F19:AI19,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL19" s="4" t="s">
@@ -3022,15 +2995,15 @@
       </c>
       <c r="AM19" s="9">
         <f>AM18-AM11</f>
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="AN19" s="9">
         <f>AN18-AN11</f>
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="AO19" s="9">
         <f>AM19+AN19</f>
-        <v>825</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3044,67 +3017,71 @@
         <v>58</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H20" s="32"/>
       <c r="I20" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N20" s="47"/>
-      <c r="O20" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N20" s="40"/>
+      <c r="O20" s="32"/>
       <c r="P20" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="31"/>
+      <c r="T20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V20" s="32"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
-      <c r="Y20" s="49"/>
+      <c r="Y20" s="30"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="31"/>
+      <c r="AC20" s="32"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
-      <c r="AF20" s="49"/>
+      <c r="AF20" s="30"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
       <c r="AJ20" s="4">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK20" s="4">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL20" s="4" t="s">
@@ -3112,15 +3089,15 @@
       </c>
       <c r="AM20" s="12">
         <f>AM19/AM18</f>
-        <v>0.71255060728744934</v>
+        <v>0.65991902834008098</v>
       </c>
       <c r="AN20" s="12">
         <f>AN19/AN18</f>
-        <v>0.86630036630036633</v>
+        <v>0.8424908424908425</v>
       </c>
       <c r="AO20" s="12">
         <f>AO19/AO18</f>
-        <v>0.79326923076923073</v>
+        <v>0.75576923076923075</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3140,61 +3117,65 @@
         <v>8</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H21" s="32"/>
       <c r="I21" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N21" s="47"/>
-      <c r="O21" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N21" s="40"/>
+      <c r="O21" s="32"/>
       <c r="P21" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="31"/>
+      <c r="T21" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V21" s="32"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
-      <c r="Y21" s="49"/>
+      <c r="Y21" s="30"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="31"/>
+      <c r="AC21" s="32"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
-      <c r="AF21" s="49"/>
+      <c r="AF21" s="30"/>
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
       <c r="AJ21" s="4">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK21" s="4">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL21" s="16"/>
@@ -3219,61 +3200,65 @@
         <v>8</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H22" s="32"/>
       <c r="I22" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="N22" s="47"/>
-      <c r="O22" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="N22" s="40"/>
+      <c r="O22" s="32"/>
       <c r="P22" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="31"/>
+      <c r="T22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V22" s="32"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
-      <c r="Y22" s="49"/>
+      <c r="Y22" s="30"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="31"/>
+      <c r="AC22" s="32"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
-      <c r="AF22" s="49"/>
+      <c r="AF22" s="30"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
       <c r="AJ22" s="4">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK22" s="4">
-        <f>COUNTIF(F22:AI22,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL22" s="16"/>
@@ -3298,61 +3283,65 @@
         <v>8</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H23" s="32"/>
       <c r="I23" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N23" s="47"/>
-      <c r="O23" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N23" s="40"/>
+      <c r="O23" s="32"/>
       <c r="P23" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="31"/>
+      <c r="T23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V23" s="32"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
-      <c r="Y23" s="49"/>
+      <c r="Y23" s="30"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-      <c r="AC23" s="31"/>
+      <c r="AC23" s="32"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
-      <c r="AF23" s="49"/>
+      <c r="AF23" s="30"/>
       <c r="AG23" s="8"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="8"/>
       <c r="AJ23" s="4">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK23" s="4">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL23" s="16"/>
@@ -3377,61 +3366,65 @@
         <v>8</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H24" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H24" s="32"/>
       <c r="I24" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N24" s="47"/>
-      <c r="O24" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N24" s="40"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="31"/>
+      <c r="T24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V24" s="32"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
-      <c r="Y24" s="49"/>
+      <c r="Y24" s="30"/>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-      <c r="AC24" s="31"/>
+      <c r="AC24" s="32"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-      <c r="AF24" s="49"/>
+      <c r="AF24" s="30"/>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
       <c r="AJ24" s="4">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK24" s="4">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL24" s="16"/>
@@ -3456,61 +3449,65 @@
         <v>8</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H25" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H25" s="32"/>
       <c r="I25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N25" s="47"/>
-      <c r="O25" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N25" s="40"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="31"/>
+      <c r="T25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V25" s="32"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
-      <c r="Y25" s="49"/>
+      <c r="Y25" s="30"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="31"/>
+      <c r="AC25" s="32"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
-      <c r="AF25" s="49"/>
+      <c r="AF25" s="30"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
       <c r="AJ25" s="4">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK25" s="4">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL25" s="16"/>
@@ -3535,61 +3532,65 @@
         <v>8</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="H26" s="32"/>
       <c r="I26" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="N26" s="47"/>
-      <c r="O26" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="N26" s="40"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="31"/>
+      <c r="T26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V26" s="32"/>
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
-      <c r="Y26" s="49"/>
+      <c r="Y26" s="30"/>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-      <c r="AC26" s="31"/>
+      <c r="AC26" s="32"/>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
-      <c r="AF26" s="49"/>
+      <c r="AF26" s="30"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
       <c r="AJ26" s="4">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK26" s="4">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL26" s="16"/>
@@ -3614,61 +3615,65 @@
         <v>8</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H27" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="H27" s="32"/>
       <c r="I27" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N27" s="47"/>
-      <c r="O27" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N27" s="40"/>
+      <c r="O27" s="32"/>
       <c r="P27" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="31"/>
+      <c r="T27" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U27" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V27" s="32"/>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
-      <c r="Y27" s="49"/>
+      <c r="Y27" s="30"/>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-      <c r="AC27" s="31"/>
+      <c r="AC27" s="32"/>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
-      <c r="AF27" s="49"/>
+      <c r="AF27" s="30"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="4">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK27" s="4">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL27" s="16"/>
@@ -3693,61 +3698,65 @@
         <v>8</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H28" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="H28" s="32"/>
       <c r="I28" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="N28" s="47"/>
-      <c r="O28" s="31"/>
+        <v>118</v>
+      </c>
+      <c r="N28" s="40"/>
+      <c r="O28" s="32"/>
       <c r="P28" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="31"/>
+      <c r="T28" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U28" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="V28" s="32"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
-      <c r="Y28" s="49"/>
+      <c r="Y28" s="30"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-      <c r="AC28" s="31"/>
+      <c r="AC28" s="32"/>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
-      <c r="AF28" s="49"/>
+      <c r="AF28" s="30"/>
       <c r="AG28" s="8"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="4">
-        <f>COUNTIF(F28:AI28,"P")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="AK28" s="4">
-        <f>COUNTIF(F28:AI28,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="AL28" s="16"/>
@@ -3764,67 +3773,71 @@
         <v>27</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H29" s="32"/>
+        <v>119</v>
+      </c>
+      <c r="H29" s="33"/>
       <c r="I29" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="N29" s="48"/>
-      <c r="O29" s="32"/>
+        <v>119</v>
+      </c>
+      <c r="N29" s="41"/>
+      <c r="O29" s="33"/>
       <c r="P29" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="32"/>
+      <c r="T29" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V29" s="33"/>
       <c r="W29" s="8"/>
       <c r="X29" s="8"/>
-      <c r="Y29" s="49"/>
+      <c r="Y29" s="30"/>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-      <c r="AC29" s="32"/>
+      <c r="AC29" s="33"/>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
-      <c r="AF29" s="49"/>
+      <c r="AF29" s="30"/>
       <c r="AG29" s="8"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
       <c r="AJ29" s="4">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK29" s="4">
-        <f>COUNTIF(F29:AI29,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL29" s="16"/>
@@ -3834,11 +3847,10 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H5:H29"/>
-    <mergeCell ref="N5:N29"/>
-    <mergeCell ref="O5:O29"/>
     <mergeCell ref="V5:V29"/>
     <mergeCell ref="AC5:AC29"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="AJ3:AJ4"/>
@@ -3849,18 +3861,24 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H29"/>
+    <mergeCell ref="N5:N29"/>
+    <mergeCell ref="O5:O29"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B29">
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6:AB29 AL4:AM4 AG6:AI29 F6:G29 I6:M29 P6:U29 W6:X29 AD6:AE29 F3:AI5">
+  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U29 W5:AB29 AD5:AI29 F6:G29 I6:M29">
+    <cfRule type="expression" dxfId="23" priority="1">
+      <formula>F$4=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI5 F6:G29 I6:M29 P6:U29 W6:X29 Z6:AB29 AD6:AE29 AG6:AI29 AL4:AM4">
     <cfRule type="expression" dxfId="22" priority="12">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6:AB29 AG6:AI29 F6:G29 I6:M29 P6:U29 W6:X29 AD6:AE29 F5:AI5">
+  <conditionalFormatting sqref="F5:AI5 F6:G29 I6:M29 P6:U29 W6:X29 Z6:AB29 AD6:AE29 AG6:AI29">
     <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
       <formula>"A"</formula>
     </cfRule>
@@ -3868,7 +3886,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AI29 F6:G29 I6:M29 P6:U29 W6:AB29 AD6:AE29 F5:AI5">
+  <conditionalFormatting sqref="F5:AI5 F6:G29 I6:M29 P6:U29 W6:AB29 AD6:AE29 AG6:AI29">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -3901,11 +3919,6 @@
   <conditionalFormatting sqref="AM17:AO17">
     <cfRule type="expression" dxfId="13" priority="6">
       <formula>AM$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI4 F6:G29 I6:M29 P5:U29 F5:O5 W5:AB29 V5 AD5:AI29 AC5">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>F$4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3961,43 +3974,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
       <c r="AJ1" s="15"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="15"/>
@@ -4006,43 +4019,43 @@
       <c r="AO1" s="15"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="37"/>
+      <c r="A2" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="46"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
       <c r="AJ2" s="15"/>
       <c r="AK2" s="15"/>
       <c r="AL2" s="15"/>
@@ -4051,19 +4064,19 @@
       <c r="AO2" s="15"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="48" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -4186,25 +4199,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="44" t="s">
+      <c r="AJ3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="44" t="s">
+      <c r="AK3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="29"/>
+      <c r="AM3" s="34"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
       <c r="F4" s="26">
         <v>45597</v>
       </c>
@@ -4295,8 +4308,8 @@
       <c r="AI4" s="26">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
+      <c r="AJ4" s="45"/>
+      <c r="AK4" s="45"/>
       <c r="AL4" s="3" t="s">
         <v>7</v>
       </c>
@@ -4323,71 +4336,75 @@
         <v>8</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H5" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N5" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="O5" s="39" t="s">
-        <v>131</v>
+      <c r="O5" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R5" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="39" t="s">
-        <v>131</v>
+      <c r="T5" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V5" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="W5" s="23"/>
       <c r="X5" s="23"/>
-      <c r="Y5" s="45"/>
+      <c r="Y5" s="29"/>
       <c r="Z5" s="23"/>
       <c r="AA5" s="23"/>
       <c r="AB5" s="23"/>
-      <c r="AC5" s="39" t="s">
-        <v>131</v>
+      <c r="AC5" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="AD5" s="23"/>
       <c r="AE5" s="23"/>
-      <c r="AF5" s="45"/>
+      <c r="AF5" s="29"/>
       <c r="AG5" s="23"/>
       <c r="AH5" s="23"/>
       <c r="AI5" s="23"/>
       <c r="AJ5" s="3">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>10</v>
+        <f t="shared" ref="AJ5:AJ35" si="1">COUNTIF(F5:AI5,"P")</f>
+        <v>12</v>
       </c>
       <c r="AK5" s="3">
-        <f>COUNTIF(F5:AI5,"A")</f>
+        <f t="shared" ref="AK5:AK35" si="2">COUNTIF(F5:AI5,"A")</f>
         <v>0</v>
       </c>
       <c r="AL5" s="4" t="s">
@@ -4418,61 +4435,65 @@
         <v>8</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H6" s="43"/>
       <c r="I6" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N6" s="40"/>
+      <c r="O6" s="43"/>
       <c r="P6" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="40"/>
+      <c r="T6" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V6" s="43"/>
       <c r="W6" s="23"/>
       <c r="X6" s="23"/>
-      <c r="Y6" s="45"/>
+      <c r="Y6" s="29"/>
       <c r="Z6" s="23"/>
       <c r="AA6" s="23"/>
       <c r="AB6" s="23"/>
-      <c r="AC6" s="40"/>
+      <c r="AC6" s="43"/>
       <c r="AD6" s="23"/>
       <c r="AE6" s="23"/>
-      <c r="AF6" s="45"/>
+      <c r="AF6" s="29"/>
       <c r="AG6" s="23"/>
       <c r="AH6" s="23"/>
       <c r="AI6" s="23"/>
       <c r="AJ6" s="3">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK6" s="3">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL6" s="4" t="s">
@@ -4501,61 +4522,65 @@
         <v>8</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H7" s="43"/>
       <c r="I7" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K7" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N7" s="40"/>
+      <c r="O7" s="43"/>
       <c r="P7" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="40"/>
+      <c r="T7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V7" s="43"/>
       <c r="W7" s="23"/>
       <c r="X7" s="23"/>
-      <c r="Y7" s="45"/>
+      <c r="Y7" s="29"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="23"/>
       <c r="AB7" s="23"/>
-      <c r="AC7" s="40"/>
+      <c r="AC7" s="43"/>
       <c r="AD7" s="23"/>
       <c r="AE7" s="23"/>
-      <c r="AF7" s="45"/>
+      <c r="AF7" s="29"/>
       <c r="AG7" s="23"/>
       <c r="AH7" s="23"/>
       <c r="AI7" s="23"/>
       <c r="AJ7" s="3">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK7" s="3">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL7" s="17"/>
@@ -4580,69 +4605,73 @@
         <v>8</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H8" s="43"/>
       <c r="I8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N8" s="40"/>
+      <c r="O8" s="43"/>
       <c r="P8" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="40"/>
+      <c r="T8" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V8" s="43"/>
       <c r="W8" s="23"/>
       <c r="X8" s="23"/>
-      <c r="Y8" s="45"/>
+      <c r="Y8" s="29"/>
       <c r="Z8" s="23"/>
       <c r="AA8" s="23"/>
       <c r="AB8" s="23"/>
-      <c r="AC8" s="40"/>
+      <c r="AC8" s="43"/>
       <c r="AD8" s="23"/>
       <c r="AE8" s="23"/>
-      <c r="AF8" s="45"/>
+      <c r="AF8" s="29"/>
       <c r="AG8" s="23"/>
       <c r="AH8" s="23"/>
       <c r="AI8" s="23"/>
       <c r="AJ8" s="3">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK8" s="3">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL8" s="29" t="s">
+      <c r="AL8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="34"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
@@ -4661,61 +4690,65 @@
         <v>8</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H9" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H9" s="43"/>
       <c r="I9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9" s="47"/>
-      <c r="O9" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N9" s="40"/>
+      <c r="O9" s="43"/>
       <c r="P9" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="40"/>
+      <c r="T9" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V9" s="43"/>
       <c r="W9" s="23"/>
       <c r="X9" s="23"/>
-      <c r="Y9" s="45"/>
+      <c r="Y9" s="29"/>
       <c r="Z9" s="23"/>
       <c r="AA9" s="23"/>
       <c r="AB9" s="23"/>
-      <c r="AC9" s="40"/>
+      <c r="AC9" s="43"/>
       <c r="AD9" s="23"/>
       <c r="AE9" s="23"/>
-      <c r="AF9" s="45"/>
+      <c r="AF9" s="29"/>
       <c r="AG9" s="23"/>
       <c r="AH9" s="23"/>
       <c r="AI9" s="23"/>
       <c r="AJ9" s="3">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK9" s="3">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL9" s="4" t="s">
@@ -4748,61 +4781,65 @@
         <v>8</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H10" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H10" s="43"/>
       <c r="I10" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K10" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N10" s="47"/>
-      <c r="O10" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N10" s="40"/>
+      <c r="O10" s="43"/>
       <c r="P10" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="40"/>
+      <c r="T10" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U10" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V10" s="43"/>
       <c r="W10" s="23"/>
       <c r="X10" s="23"/>
-      <c r="Y10" s="45"/>
+      <c r="Y10" s="29"/>
       <c r="Z10" s="23"/>
       <c r="AA10" s="23"/>
       <c r="AB10" s="23"/>
-      <c r="AC10" s="40"/>
+      <c r="AC10" s="43"/>
       <c r="AD10" s="23"/>
       <c r="AE10" s="23"/>
-      <c r="AF10" s="45"/>
+      <c r="AF10" s="29"/>
       <c r="AG10" s="23"/>
       <c r="AH10" s="23"/>
       <c r="AI10" s="23"/>
       <c r="AJ10" s="3">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK10" s="3">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL10" s="4" t="s">
@@ -4838,61 +4875,65 @@
         <v>8</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H11" s="43"/>
       <c r="I11" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K11" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M11" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N11" s="47"/>
-      <c r="O11" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N11" s="40"/>
+      <c r="O11" s="43"/>
       <c r="P11" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="40"/>
+      <c r="T11" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U11" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V11" s="43"/>
       <c r="W11" s="23"/>
       <c r="X11" s="23"/>
-      <c r="Y11" s="45"/>
+      <c r="Y11" s="29"/>
       <c r="Z11" s="23"/>
       <c r="AA11" s="23"/>
       <c r="AB11" s="23"/>
-      <c r="AC11" s="40"/>
+      <c r="AC11" s="43"/>
       <c r="AD11" s="23"/>
       <c r="AE11" s="23"/>
-      <c r="AF11" s="45"/>
+      <c r="AF11" s="29"/>
       <c r="AG11" s="23"/>
       <c r="AH11" s="23"/>
       <c r="AI11" s="23"/>
       <c r="AJ11" s="3">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK11" s="3">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL11" s="4" t="s">
@@ -4900,15 +4941,15 @@
       </c>
       <c r="AM11" s="9">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28</f>
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="AN11" s="9">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AO11" s="9">
         <f>AM11+AN11</f>
-        <v>196</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -4928,61 +4969,65 @@
         <v>8</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H12" s="43"/>
       <c r="I12" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L12" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N12" s="40"/>
+      <c r="O12" s="43"/>
       <c r="P12" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="40"/>
+      <c r="T12" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U12" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V12" s="43"/>
       <c r="W12" s="23"/>
       <c r="X12" s="23"/>
-      <c r="Y12" s="45"/>
+      <c r="Y12" s="29"/>
       <c r="Z12" s="23"/>
       <c r="AA12" s="23"/>
       <c r="AB12" s="23"/>
-      <c r="AC12" s="40"/>
+      <c r="AC12" s="43"/>
       <c r="AD12" s="23"/>
       <c r="AE12" s="23"/>
-      <c r="AF12" s="45"/>
+      <c r="AF12" s="29"/>
       <c r="AG12" s="23"/>
       <c r="AH12" s="23"/>
       <c r="AI12" s="23"/>
       <c r="AJ12" s="3">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK12" s="3">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL12" s="4" t="s">
@@ -4990,15 +5035,15 @@
       </c>
       <c r="AM12" s="9">
         <f>AM11/AM10</f>
-        <v>0.26923076923076922</v>
+        <v>0.32591093117408909</v>
       </c>
       <c r="AN12" s="9">
         <f>AN11/AN10</f>
-        <v>0.11538461538461539</v>
+        <v>0.13736263736263737</v>
       </c>
       <c r="AO12" s="9">
         <f>AO11/AO10</f>
-        <v>0.18846153846153846</v>
+        <v>0.22692307692307692</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5018,61 +5063,65 @@
         <v>8</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H13" s="43"/>
       <c r="I13" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N13" s="47"/>
-      <c r="O13" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N13" s="40"/>
+      <c r="O13" s="43"/>
       <c r="P13" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="40"/>
+      <c r="T13" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V13" s="43"/>
       <c r="W13" s="23"/>
       <c r="X13" s="23"/>
-      <c r="Y13" s="45"/>
+      <c r="Y13" s="29"/>
       <c r="Z13" s="23"/>
       <c r="AA13" s="23"/>
       <c r="AB13" s="23"/>
-      <c r="AC13" s="40"/>
+      <c r="AC13" s="43"/>
       <c r="AD13" s="23"/>
       <c r="AE13" s="23"/>
-      <c r="AF13" s="45"/>
+      <c r="AF13" s="29"/>
       <c r="AG13" s="23"/>
       <c r="AH13" s="23"/>
       <c r="AI13" s="23"/>
       <c r="AJ13" s="3">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK13" s="3">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL13" s="17"/>
@@ -5097,61 +5146,65 @@
         <v>8</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H14" s="43"/>
       <c r="I14" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M14" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N14" s="47"/>
-      <c r="O14" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N14" s="40"/>
+      <c r="O14" s="43"/>
       <c r="P14" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="40"/>
+      <c r="T14" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V14" s="43"/>
       <c r="W14" s="23"/>
       <c r="X14" s="23"/>
-      <c r="Y14" s="45"/>
+      <c r="Y14" s="29"/>
       <c r="Z14" s="23"/>
       <c r="AA14" s="23"/>
       <c r="AB14" s="23"/>
-      <c r="AC14" s="40"/>
+      <c r="AC14" s="43"/>
       <c r="AD14" s="23"/>
       <c r="AE14" s="23"/>
-      <c r="AF14" s="45"/>
+      <c r="AF14" s="29"/>
       <c r="AG14" s="23"/>
       <c r="AH14" s="23"/>
       <c r="AI14" s="23"/>
       <c r="AJ14" s="3">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK14" s="3">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL14" s="20"/>
@@ -5176,61 +5229,65 @@
         <v>8</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H15" s="43"/>
       <c r="I15" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K15" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L15" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M15" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N15" s="47"/>
-      <c r="O15" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N15" s="40"/>
+      <c r="O15" s="43"/>
       <c r="P15" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R15" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="40"/>
+      <c r="T15" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V15" s="43"/>
       <c r="W15" s="23"/>
       <c r="X15" s="23"/>
-      <c r="Y15" s="45"/>
+      <c r="Y15" s="29"/>
       <c r="Z15" s="23"/>
       <c r="AA15" s="23"/>
       <c r="AB15" s="23"/>
-      <c r="AC15" s="40"/>
+      <c r="AC15" s="43"/>
       <c r="AD15" s="23"/>
       <c r="AE15" s="23"/>
-      <c r="AF15" s="45"/>
+      <c r="AF15" s="29"/>
       <c r="AG15" s="23"/>
       <c r="AH15" s="23"/>
       <c r="AI15" s="23"/>
       <c r="AJ15" s="3">
-        <f>COUNTIF(F15:AI15,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AK15" s="3">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL15" s="17"/>
@@ -5255,69 +5312,73 @@
         <v>8</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H16" s="43"/>
       <c r="I16" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K16" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M16" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N16" s="47"/>
-      <c r="O16" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N16" s="40"/>
+      <c r="O16" s="43"/>
       <c r="P16" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q16" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R16" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="40"/>
+      <c r="T16" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U16" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V16" s="43"/>
       <c r="W16" s="23"/>
       <c r="X16" s="23"/>
-      <c r="Y16" s="45"/>
+      <c r="Y16" s="29"/>
       <c r="Z16" s="23"/>
       <c r="AA16" s="23"/>
       <c r="AB16" s="23"/>
-      <c r="AC16" s="40"/>
+      <c r="AC16" s="43"/>
       <c r="AD16" s="23"/>
       <c r="AE16" s="23"/>
-      <c r="AF16" s="45"/>
+      <c r="AF16" s="29"/>
       <c r="AG16" s="23"/>
       <c r="AH16" s="23"/>
       <c r="AI16" s="23"/>
       <c r="AJ16" s="3">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK16" s="3">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AL16" s="29" t="s">
+      <c r="AL16" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="29"/>
+      <c r="AM16" s="34"/>
+      <c r="AN16" s="34"/>
+      <c r="AO16" s="34"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
@@ -5336,61 +5397,65 @@
         <v>8</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H17" s="43"/>
       <c r="I17" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K17" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M17" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="47"/>
-      <c r="O17" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N17" s="40"/>
+      <c r="O17" s="43"/>
       <c r="P17" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q17" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R17" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="40"/>
+      <c r="T17" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="U17" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V17" s="43"/>
       <c r="W17" s="23"/>
       <c r="X17" s="23"/>
-      <c r="Y17" s="45"/>
+      <c r="Y17" s="29"/>
       <c r="Z17" s="23"/>
       <c r="AA17" s="23"/>
       <c r="AB17" s="23"/>
-      <c r="AC17" s="40"/>
+      <c r="AC17" s="43"/>
       <c r="AD17" s="23"/>
       <c r="AE17" s="23"/>
-      <c r="AF17" s="45"/>
+      <c r="AF17" s="29"/>
       <c r="AG17" s="23"/>
       <c r="AH17" s="23"/>
       <c r="AI17" s="23"/>
       <c r="AJ17" s="3">
-        <f>COUNTIF(F17:AI17,"P")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="AK17" s="3">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="AL17" s="4" t="s">
@@ -5423,61 +5488,65 @@
         <v>8</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H18" s="43"/>
       <c r="I18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N18" s="47"/>
-      <c r="O18" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N18" s="40"/>
+      <c r="O18" s="43"/>
       <c r="P18" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R18" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="40"/>
+      <c r="T18" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U18" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V18" s="43"/>
       <c r="W18" s="23"/>
       <c r="X18" s="23"/>
-      <c r="Y18" s="45"/>
+      <c r="Y18" s="29"/>
       <c r="Z18" s="23"/>
       <c r="AA18" s="23"/>
       <c r="AB18" s="23"/>
-      <c r="AC18" s="40"/>
+      <c r="AC18" s="43"/>
       <c r="AD18" s="23"/>
       <c r="AE18" s="23"/>
-      <c r="AF18" s="45"/>
+      <c r="AF18" s="29"/>
       <c r="AG18" s="23"/>
       <c r="AH18" s="23"/>
       <c r="AI18" s="23"/>
       <c r="AJ18" s="3">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK18" s="3">
-        <f>COUNTIF(F18:AI18,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL18" s="4" t="s">
@@ -5513,61 +5582,65 @@
         <v>8</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H19" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H19" s="43"/>
       <c r="I19" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L19" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N19" s="47"/>
-      <c r="O19" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N19" s="40"/>
+      <c r="O19" s="43"/>
       <c r="P19" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q19" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R19" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="40"/>
+      <c r="T19" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U19" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V19" s="43"/>
       <c r="W19" s="23"/>
       <c r="X19" s="23"/>
-      <c r="Y19" s="45"/>
+      <c r="Y19" s="29"/>
       <c r="Z19" s="23"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="23"/>
-      <c r="AC19" s="40"/>
+      <c r="AC19" s="43"/>
       <c r="AD19" s="23"/>
       <c r="AE19" s="23"/>
-      <c r="AF19" s="45"/>
+      <c r="AF19" s="29"/>
       <c r="AG19" s="23"/>
       <c r="AH19" s="23"/>
       <c r="AI19" s="23"/>
       <c r="AJ19" s="3">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK19" s="3">
-        <f>COUNTIF(F19:AI19,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL19" s="4" t="s">
@@ -5575,15 +5648,15 @@
       </c>
       <c r="AM19" s="9">
         <f>AM18-AM11</f>
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="AN19" s="9">
         <f>AN18-AN11</f>
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="AO19" s="9">
         <f>AM19+AN19</f>
-        <v>844</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5603,61 +5676,65 @@
         <v>8</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H20" s="43"/>
       <c r="I20" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K20" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L20" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N20" s="47"/>
-      <c r="O20" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N20" s="40"/>
+      <c r="O20" s="43"/>
       <c r="P20" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q20" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R20" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="40"/>
+      <c r="T20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V20" s="43"/>
       <c r="W20" s="23"/>
       <c r="X20" s="23"/>
-      <c r="Y20" s="45"/>
+      <c r="Y20" s="29"/>
       <c r="Z20" s="23"/>
       <c r="AA20" s="23"/>
       <c r="AB20" s="23"/>
-      <c r="AC20" s="40"/>
+      <c r="AC20" s="43"/>
       <c r="AD20" s="23"/>
       <c r="AE20" s="23"/>
-      <c r="AF20" s="45"/>
+      <c r="AF20" s="29"/>
       <c r="AG20" s="23"/>
       <c r="AH20" s="23"/>
       <c r="AI20" s="23"/>
       <c r="AJ20" s="3">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK20" s="3">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL20" s="4" t="s">
@@ -5665,15 +5742,15 @@
       </c>
       <c r="AM20" s="12">
         <f>AM19/AM18</f>
-        <v>0.73076923076923073</v>
+        <v>0.67408906882591091</v>
       </c>
       <c r="AN20" s="12">
         <f>AN19/AN18</f>
-        <v>0.88461538461538458</v>
+        <v>0.86263736263736268</v>
       </c>
       <c r="AO20" s="12">
         <f>AO19/AO18</f>
-        <v>0.81153846153846154</v>
+        <v>0.77307692307692311</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5693,61 +5770,65 @@
         <v>8</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H21" s="43"/>
       <c r="I21" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K21" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L21" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N21" s="47"/>
-      <c r="O21" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N21" s="40"/>
+      <c r="O21" s="43"/>
       <c r="P21" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R21" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="40"/>
+      <c r="T21" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U21" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V21" s="43"/>
       <c r="W21" s="23"/>
       <c r="X21" s="23"/>
-      <c r="Y21" s="45"/>
+      <c r="Y21" s="29"/>
       <c r="Z21" s="23"/>
       <c r="AA21" s="23"/>
       <c r="AB21" s="23"/>
-      <c r="AC21" s="40"/>
+      <c r="AC21" s="43"/>
       <c r="AD21" s="23"/>
       <c r="AE21" s="23"/>
-      <c r="AF21" s="45"/>
+      <c r="AF21" s="29"/>
       <c r="AG21" s="23"/>
       <c r="AH21" s="23"/>
       <c r="AI21" s="23"/>
       <c r="AJ21" s="3">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK21" s="3">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL21" s="15"/>
@@ -5772,61 +5853,65 @@
         <v>8</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H22" s="43"/>
       <c r="I22" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K22" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L22" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N22" s="47"/>
-      <c r="O22" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N22" s="40"/>
+      <c r="O22" s="43"/>
       <c r="P22" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q22" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="40"/>
+      <c r="T22" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U22" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V22" s="43"/>
       <c r="W22" s="23"/>
       <c r="X22" s="23"/>
-      <c r="Y22" s="45"/>
+      <c r="Y22" s="29"/>
       <c r="Z22" s="23"/>
       <c r="AA22" s="23"/>
       <c r="AB22" s="23"/>
-      <c r="AC22" s="40"/>
+      <c r="AC22" s="43"/>
       <c r="AD22" s="23"/>
       <c r="AE22" s="23"/>
-      <c r="AF22" s="45"/>
+      <c r="AF22" s="29"/>
       <c r="AG22" s="23"/>
       <c r="AH22" s="23"/>
       <c r="AI22" s="23"/>
       <c r="AJ22" s="3">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK22" s="3">
-        <f>COUNTIF(F22:AI22,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL22" s="15"/>
@@ -5851,61 +5936,65 @@
         <v>8</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H23" s="43"/>
       <c r="I23" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K23" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L23" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N23" s="47"/>
-      <c r="O23" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N23" s="40"/>
+      <c r="O23" s="43"/>
       <c r="P23" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q23" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="40"/>
+      <c r="T23" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U23" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V23" s="43"/>
       <c r="W23" s="23"/>
       <c r="X23" s="23"/>
-      <c r="Y23" s="45"/>
+      <c r="Y23" s="29"/>
       <c r="Z23" s="23"/>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
-      <c r="AC23" s="40"/>
+      <c r="AC23" s="43"/>
       <c r="AD23" s="23"/>
       <c r="AE23" s="23"/>
-      <c r="AF23" s="45"/>
+      <c r="AF23" s="29"/>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
       <c r="AI23" s="23"/>
       <c r="AJ23" s="3">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="AK23" s="3">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AL23" s="15"/>
@@ -5930,61 +6019,65 @@
         <v>8</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H24" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H24" s="43"/>
       <c r="I24" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K24" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L24" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N24" s="47"/>
-      <c r="O24" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N24" s="40"/>
+      <c r="O24" s="43"/>
       <c r="P24" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q24" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R24" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="40"/>
+      <c r="T24" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U24" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V24" s="43"/>
       <c r="W24" s="23"/>
       <c r="X24" s="23"/>
-      <c r="Y24" s="45"/>
+      <c r="Y24" s="29"/>
       <c r="Z24" s="23"/>
       <c r="AA24" s="23"/>
       <c r="AB24" s="23"/>
-      <c r="AC24" s="40"/>
+      <c r="AC24" s="43"/>
       <c r="AD24" s="23"/>
       <c r="AE24" s="23"/>
-      <c r="AF24" s="45"/>
+      <c r="AF24" s="29"/>
       <c r="AG24" s="23"/>
       <c r="AH24" s="23"/>
       <c r="AI24" s="23"/>
       <c r="AJ24" s="3">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK24" s="3">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL24" s="15"/>
@@ -6009,61 +6102,65 @@
         <v>8</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H25" s="43"/>
       <c r="I25" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K25" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L25" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N25" s="47"/>
-      <c r="O25" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N25" s="40"/>
+      <c r="O25" s="43"/>
       <c r="P25" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q25" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R25" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="40"/>
+      <c r="T25" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U25" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V25" s="43"/>
       <c r="W25" s="23"/>
       <c r="X25" s="23"/>
-      <c r="Y25" s="45"/>
+      <c r="Y25" s="29"/>
       <c r="Z25" s="23"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="23"/>
-      <c r="AC25" s="40"/>
+      <c r="AC25" s="43"/>
       <c r="AD25" s="23"/>
       <c r="AE25" s="23"/>
-      <c r="AF25" s="45"/>
+      <c r="AF25" s="29"/>
       <c r="AG25" s="23"/>
       <c r="AH25" s="23"/>
       <c r="AI25" s="23"/>
       <c r="AJ25" s="3">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="AK25" s="3">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="AL25" s="15"/>
@@ -6088,61 +6185,65 @@
         <v>8</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H26" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H26" s="43"/>
       <c r="I26" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K26" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L26" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M26" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N26" s="47"/>
-      <c r="O26" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N26" s="40"/>
+      <c r="O26" s="43"/>
       <c r="P26" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="40"/>
+      <c r="T26" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U26" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V26" s="43"/>
       <c r="W26" s="23"/>
       <c r="X26" s="23"/>
-      <c r="Y26" s="45"/>
+      <c r="Y26" s="29"/>
       <c r="Z26" s="23"/>
       <c r="AA26" s="23"/>
       <c r="AB26" s="23"/>
-      <c r="AC26" s="40"/>
+      <c r="AC26" s="43"/>
       <c r="AD26" s="23"/>
       <c r="AE26" s="23"/>
-      <c r="AF26" s="45"/>
+      <c r="AF26" s="29"/>
       <c r="AG26" s="23"/>
       <c r="AH26" s="23"/>
       <c r="AI26" s="23"/>
       <c r="AJ26" s="3">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="AK26" s="3">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="AL26" s="15"/>
@@ -6167,61 +6268,65 @@
         <v>8</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H27" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H27" s="43"/>
       <c r="I27" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K27" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L27" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M27" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N27" s="47"/>
-      <c r="O27" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N27" s="40"/>
+      <c r="O27" s="43"/>
       <c r="P27" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q27" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R27" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="40"/>
+      <c r="T27" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U27" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V27" s="43"/>
       <c r="W27" s="23"/>
       <c r="X27" s="23"/>
-      <c r="Y27" s="45"/>
+      <c r="Y27" s="29"/>
       <c r="Z27" s="23"/>
       <c r="AA27" s="23"/>
       <c r="AB27" s="23"/>
-      <c r="AC27" s="40"/>
+      <c r="AC27" s="43"/>
       <c r="AD27" s="23"/>
       <c r="AE27" s="23"/>
-      <c r="AF27" s="45"/>
+      <c r="AF27" s="29"/>
       <c r="AG27" s="23"/>
       <c r="AH27" s="23"/>
       <c r="AI27" s="23"/>
       <c r="AJ27" s="3">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK27" s="3">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL27" s="15"/>
@@ -6237,7 +6342,7 @@
         <v>140</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="25" t="s">
         <v>114</v>
@@ -6246,61 +6351,65 @@
         <v>8</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H28" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H28" s="43"/>
       <c r="I28" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K28" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M28" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N28" s="47"/>
-      <c r="O28" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N28" s="40"/>
+      <c r="O28" s="43"/>
       <c r="P28" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R28" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="40"/>
+      <c r="T28" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U28" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V28" s="43"/>
       <c r="W28" s="23"/>
       <c r="X28" s="23"/>
-      <c r="Y28" s="45"/>
+      <c r="Y28" s="29"/>
       <c r="Z28" s="23"/>
       <c r="AA28" s="23"/>
       <c r="AB28" s="23"/>
-      <c r="AC28" s="40"/>
+      <c r="AC28" s="43"/>
       <c r="AD28" s="23"/>
       <c r="AE28" s="23"/>
-      <c r="AF28" s="45"/>
+      <c r="AF28" s="29"/>
       <c r="AG28" s="23"/>
       <c r="AH28" s="23"/>
       <c r="AI28" s="23"/>
       <c r="AJ28" s="3">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK28" s="3">
-        <f>COUNTIF(F28:AI28,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL28" s="15"/>
@@ -6325,61 +6434,65 @@
         <v>8</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H29" s="43"/>
       <c r="I29" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K29" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L29" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M29" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N29" s="47"/>
-      <c r="O29" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N29" s="40"/>
+      <c r="O29" s="43"/>
       <c r="P29" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="40"/>
+      <c r="T29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V29" s="43"/>
       <c r="W29" s="23"/>
       <c r="X29" s="23"/>
-      <c r="Y29" s="45"/>
+      <c r="Y29" s="29"/>
       <c r="Z29" s="23"/>
       <c r="AA29" s="23"/>
       <c r="AB29" s="23"/>
-      <c r="AC29" s="40"/>
+      <c r="AC29" s="43"/>
       <c r="AD29" s="23"/>
       <c r="AE29" s="23"/>
-      <c r="AF29" s="45"/>
+      <c r="AF29" s="29"/>
       <c r="AG29" s="23"/>
       <c r="AH29" s="23"/>
       <c r="AI29" s="23"/>
       <c r="AJ29" s="3">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK29" s="3">
-        <f>COUNTIF(F29:AI29,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL29" s="15"/>
@@ -6402,61 +6515,65 @@
         <v>8</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H30" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H30" s="43"/>
       <c r="I30" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K30" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L30" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M30" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N30" s="47"/>
-      <c r="O30" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N30" s="40"/>
+      <c r="O30" s="43"/>
       <c r="P30" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="40"/>
+      <c r="T30" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U30" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V30" s="43"/>
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
-      <c r="Y30" s="45"/>
+      <c r="Y30" s="29"/>
       <c r="Z30" s="23"/>
       <c r="AA30" s="23"/>
       <c r="AB30" s="23"/>
-      <c r="AC30" s="40"/>
+      <c r="AC30" s="43"/>
       <c r="AD30" s="23"/>
       <c r="AE30" s="23"/>
-      <c r="AF30" s="45"/>
+      <c r="AF30" s="29"/>
       <c r="AG30" s="23"/>
       <c r="AH30" s="23"/>
       <c r="AI30" s="23"/>
       <c r="AJ30" s="3">
-        <f>COUNTIF(F30:AI30,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK30" s="3">
-        <f>COUNTIF(F30:AI30,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL30" s="15"/>
@@ -6470,70 +6587,74 @@
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="23" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H31" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H31" s="43"/>
       <c r="I31" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K31" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L31" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M31" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N31" s="47"/>
-      <c r="O31" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N31" s="40"/>
+      <c r="O31" s="43"/>
       <c r="P31" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="40"/>
+      <c r="T31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V31" s="43"/>
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
-      <c r="Y31" s="45"/>
+      <c r="Y31" s="29"/>
       <c r="Z31" s="23"/>
       <c r="AA31" s="23"/>
       <c r="AB31" s="23"/>
-      <c r="AC31" s="40"/>
+      <c r="AC31" s="43"/>
       <c r="AD31" s="23"/>
       <c r="AE31" s="23"/>
-      <c r="AF31" s="45"/>
+      <c r="AF31" s="29"/>
       <c r="AG31" s="23"/>
       <c r="AH31" s="23"/>
       <c r="AI31" s="23"/>
       <c r="AJ31" s="3">
-        <f>COUNTIF(F31:AI31,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK31" s="3">
-        <f>COUNTIF(F31:AI31,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL31" s="15"/>
@@ -6547,70 +6668,74 @@
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E32" s="23" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H32" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H32" s="43"/>
       <c r="I32" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N32" s="47"/>
-      <c r="O32" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N32" s="40"/>
+      <c r="O32" s="43"/>
       <c r="P32" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R32" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="40"/>
+      <c r="T32" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U32" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V32" s="43"/>
       <c r="W32" s="23"/>
       <c r="X32" s="23"/>
-      <c r="Y32" s="45"/>
+      <c r="Y32" s="29"/>
       <c r="Z32" s="23"/>
       <c r="AA32" s="23"/>
       <c r="AB32" s="23"/>
-      <c r="AC32" s="40"/>
+      <c r="AC32" s="43"/>
       <c r="AD32" s="23"/>
       <c r="AE32" s="23"/>
-      <c r="AF32" s="45"/>
+      <c r="AF32" s="29"/>
       <c r="AG32" s="23"/>
       <c r="AH32" s="23"/>
       <c r="AI32" s="23"/>
       <c r="AJ32" s="3">
-        <f>COUNTIF(F32:AI32,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK32" s="3">
-        <f>COUNTIF(F32:AI32,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL32" s="15"/>
@@ -6626,70 +6751,74 @@
         <v>72</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" s="23" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="H33" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="H33" s="43"/>
       <c r="I33" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J33" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K33" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L33" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M33" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N33" s="47"/>
-      <c r="O33" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="N33" s="40"/>
+      <c r="O33" s="43"/>
       <c r="P33" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R33" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="40"/>
+      <c r="T33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V33" s="43"/>
       <c r="W33" s="23"/>
       <c r="X33" s="23"/>
-      <c r="Y33" s="45"/>
+      <c r="Y33" s="29"/>
       <c r="Z33" s="23"/>
       <c r="AA33" s="23"/>
       <c r="AB33" s="23"/>
-      <c r="AC33" s="40"/>
+      <c r="AC33" s="43"/>
       <c r="AD33" s="23"/>
       <c r="AE33" s="23"/>
-      <c r="AF33" s="45"/>
+      <c r="AF33" s="29"/>
       <c r="AG33" s="23"/>
       <c r="AH33" s="23"/>
       <c r="AI33" s="23"/>
       <c r="AJ33" s="3">
-        <f>COUNTIF(F33:AI33,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK33" s="3">
-        <f>COUNTIF(F33:AI33,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL33" s="15"/>
@@ -6705,7 +6834,7 @@
         <v>92</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>102</v>
@@ -6714,61 +6843,65 @@
         <v>8</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="40"/>
+        <v>118</v>
+      </c>
+      <c r="H34" s="43"/>
       <c r="I34" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J34" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K34" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L34" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M34" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N34" s="47"/>
-      <c r="O34" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="N34" s="40"/>
+      <c r="O34" s="43"/>
       <c r="P34" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="40"/>
+      <c r="T34" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U34" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V34" s="43"/>
       <c r="W34" s="23"/>
       <c r="X34" s="23"/>
-      <c r="Y34" s="45"/>
+      <c r="Y34" s="29"/>
       <c r="Z34" s="23"/>
       <c r="AA34" s="23"/>
       <c r="AB34" s="23"/>
-      <c r="AC34" s="40"/>
+      <c r="AC34" s="43"/>
       <c r="AD34" s="23"/>
       <c r="AE34" s="23"/>
-      <c r="AF34" s="45"/>
+      <c r="AF34" s="29"/>
       <c r="AG34" s="23"/>
       <c r="AH34" s="23"/>
       <c r="AI34" s="23"/>
       <c r="AJ34" s="3">
-        <f>COUNTIF(F34:AI34,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK34" s="3">
-        <f>COUNTIF(F34:AI34,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL34" s="15"/>
@@ -6785,67 +6918,71 @@
         <v>116</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E35" s="23" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" s="41"/>
+        <v>118</v>
+      </c>
+      <c r="H35" s="44"/>
       <c r="I35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M35" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N35" s="48"/>
-      <c r="O35" s="41"/>
+        <v>118</v>
+      </c>
+      <c r="N35" s="41"/>
+      <c r="O35" s="44"/>
       <c r="P35" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="41"/>
+      <c r="T35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="U35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="V35" s="44"/>
       <c r="W35" s="23"/>
       <c r="X35" s="23"/>
-      <c r="Y35" s="45"/>
+      <c r="Y35" s="29"/>
       <c r="Z35" s="23"/>
       <c r="AA35" s="23"/>
       <c r="AB35" s="23"/>
-      <c r="AC35" s="41"/>
+      <c r="AC35" s="44"/>
       <c r="AD35" s="23"/>
       <c r="AE35" s="23"/>
-      <c r="AF35" s="45"/>
+      <c r="AF35" s="29"/>
       <c r="AG35" s="23"/>
       <c r="AH35" s="23"/>
       <c r="AI35" s="23"/>
       <c r="AJ35" s="3">
-        <f>COUNTIF(F35:AI35,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK35" s="3">
-        <f>COUNTIF(F35:AI35,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL35" s="15"/>
@@ -6855,13 +6992,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="H5:H35"/>
-    <mergeCell ref="N5:N35"/>
-    <mergeCell ref="O5:O35"/>
-    <mergeCell ref="V5:V35"/>
-    <mergeCell ref="AC5:AC35"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AM3"/>
@@ -6872,65 +7002,72 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H35"/>
+    <mergeCell ref="N5:N35"/>
+    <mergeCell ref="O5:O35"/>
+    <mergeCell ref="V5:V35"/>
+    <mergeCell ref="AC5:AC35"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z6:AB35 AG6:AI35 F6:G35 I6:M35 P6:U35 W6:X35 AD6:AE35 F3:AI5">
-    <cfRule type="expression" dxfId="36" priority="17">
+  <conditionalFormatting sqref="B5:B33">
+    <cfRule type="duplicateValues" dxfId="12" priority="301"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:O5 V5 AC5 P5:U35 W5:AB35 AD5:AI35 F6:G35 I6:M35">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U35 W5:AB35 AD5:AI35 F6:G35 I6:M35">
+    <cfRule type="expression" dxfId="10" priority="7">
+      <formula>F$4=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI5 F6:G35 I6:M35 P6:U35 W6:X35 Z6:AB35 AD6:AE35 AG6:AI35">
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6:AB35 AG6:AI35 F6:G35 I6:M35 P6:U35 W6:X35 AD6:AE35 F5:AI5">
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
+  <conditionalFormatting sqref="F5:AI5 F6:G35 I6:M35 P6:U35 W6:X35 Z6:AB35 AD6:AE35 AG6:AI35">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G35 I6:M35 P5:U35 F5:O5 W5:AB35 V5 AD5:AI35 AC5">
-    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK35">
-    <cfRule type="expression" dxfId="32" priority="18">
+    <cfRule type="expression" dxfId="6" priority="18">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G35 I6:M35 P5:U35 F5:O5 W5:AB35 V5 AD5:AI35 AC5 F3:AI4">
-    <cfRule type="expression" dxfId="31" priority="7">
-      <formula>F$4=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B33">
-    <cfRule type="duplicateValues" dxfId="30" priority="301"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL4:AM4">
-    <cfRule type="expression" dxfId="29" priority="6">
-      <formula>AL$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="28" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>AL$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL4:AM4">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="25" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (Deffodils)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C0F447-25F9-4293-8B2C-F754F827C823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5FA14D-966F-4AC5-97A1-D2A9EF9C05C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -764,15 +764,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -787,6 +778,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3847,6 +3847,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="O5:O29"/>
     <mergeCell ref="V5:V29"/>
     <mergeCell ref="AC5:AC29"/>
     <mergeCell ref="AL8:AO8"/>
@@ -3863,7 +3864,6 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="H5:H29"/>
     <mergeCell ref="N5:N29"/>
-    <mergeCell ref="O5:O29"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B29">
     <cfRule type="duplicateValues" dxfId="24" priority="22"/>
@@ -3974,43 +3974,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="44"/>
+      <c r="AF1" s="44"/>
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="44"/>
+      <c r="AI1" s="44"/>
       <c r="AJ1" s="15"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="15"/>
@@ -4019,43 +4019,43 @@
       <c r="AO1" s="15"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
       <c r="AJ2" s="15"/>
       <c r="AK2" s="15"/>
       <c r="AL2" s="15"/>
@@ -4064,19 +4064,19 @@
       <c r="AO2" s="15"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="45" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -4199,10 +4199,10 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="45" t="s">
+      <c r="AJ3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="45" t="s">
+      <c r="AK3" s="42" t="s">
         <v>6</v>
       </c>
       <c r="AL3" s="34" t="s">
@@ -4213,11 +4213,11 @@
       <c r="AO3" s="17"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
       <c r="F4" s="26">
         <v>45597</v>
       </c>
@@ -4308,8 +4308,8 @@
       <c r="AI4" s="26">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="45"/>
-      <c r="AK4" s="45"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
       <c r="AL4" s="3" t="s">
         <v>7</v>
       </c>
@@ -4341,7 +4341,7 @@
       <c r="G5" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="47" t="s">
         <v>130</v>
       </c>
       <c r="I5" s="28" t="s">
@@ -4362,7 +4362,7 @@
       <c r="N5" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="O5" s="42" t="s">
+      <c r="O5" s="47" t="s">
         <v>130</v>
       </c>
       <c r="P5" s="23" t="s">
@@ -4381,7 +4381,7 @@
       <c r="U5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="V5" s="47" t="s">
         <v>130</v>
       </c>
       <c r="W5" s="23"/>
@@ -4390,7 +4390,7 @@
       <c r="Z5" s="23"/>
       <c r="AA5" s="23"/>
       <c r="AB5" s="23"/>
-      <c r="AC5" s="42" t="s">
+      <c r="AC5" s="47" t="s">
         <v>130</v>
       </c>
       <c r="AD5" s="23"/>
@@ -4440,7 +4440,7 @@
       <c r="G6" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="43"/>
+      <c r="H6" s="48"/>
       <c r="I6" s="28" t="s">
         <v>118</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>118</v>
       </c>
       <c r="N6" s="40"/>
-      <c r="O6" s="43"/>
+      <c r="O6" s="48"/>
       <c r="P6" s="23" t="s">
         <v>118</v>
       </c>
@@ -4474,14 +4474,14 @@
       <c r="U6" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V6" s="43"/>
+      <c r="V6" s="48"/>
       <c r="W6" s="23"/>
       <c r="X6" s="23"/>
       <c r="Y6" s="29"/>
       <c r="Z6" s="23"/>
       <c r="AA6" s="23"/>
       <c r="AB6" s="23"/>
-      <c r="AC6" s="43"/>
+      <c r="AC6" s="48"/>
       <c r="AD6" s="23"/>
       <c r="AE6" s="23"/>
       <c r="AF6" s="29"/>
@@ -4527,7 +4527,7 @@
       <c r="G7" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H7" s="43"/>
+      <c r="H7" s="48"/>
       <c r="I7" s="28" t="s">
         <v>118</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>118</v>
       </c>
       <c r="N7" s="40"/>
-      <c r="O7" s="43"/>
+      <c r="O7" s="48"/>
       <c r="P7" s="23" t="s">
         <v>118</v>
       </c>
@@ -4561,14 +4561,14 @@
       <c r="U7" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V7" s="43"/>
+      <c r="V7" s="48"/>
       <c r="W7" s="23"/>
       <c r="X7" s="23"/>
       <c r="Y7" s="29"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="23"/>
       <c r="AB7" s="23"/>
-      <c r="AC7" s="43"/>
+      <c r="AC7" s="48"/>
       <c r="AD7" s="23"/>
       <c r="AE7" s="23"/>
       <c r="AF7" s="29"/>
@@ -4610,7 +4610,7 @@
       <c r="G8" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H8" s="43"/>
+      <c r="H8" s="48"/>
       <c r="I8" s="28" t="s">
         <v>118</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>118</v>
       </c>
       <c r="N8" s="40"/>
-      <c r="O8" s="43"/>
+      <c r="O8" s="48"/>
       <c r="P8" s="23" t="s">
         <v>118</v>
       </c>
@@ -4644,14 +4644,14 @@
       <c r="U8" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V8" s="43"/>
+      <c r="V8" s="48"/>
       <c r="W8" s="23"/>
       <c r="X8" s="23"/>
       <c r="Y8" s="29"/>
       <c r="Z8" s="23"/>
       <c r="AA8" s="23"/>
       <c r="AB8" s="23"/>
-      <c r="AC8" s="43"/>
+      <c r="AC8" s="48"/>
       <c r="AD8" s="23"/>
       <c r="AE8" s="23"/>
       <c r="AF8" s="29"/>
@@ -4695,7 +4695,7 @@
       <c r="G9" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="43"/>
+      <c r="H9" s="48"/>
       <c r="I9" s="28" t="s">
         <v>118</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>118</v>
       </c>
       <c r="N9" s="40"/>
-      <c r="O9" s="43"/>
+      <c r="O9" s="48"/>
       <c r="P9" s="23" t="s">
         <v>120</v>
       </c>
@@ -4729,14 +4729,14 @@
       <c r="U9" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V9" s="43"/>
+      <c r="V9" s="48"/>
       <c r="W9" s="23"/>
       <c r="X9" s="23"/>
       <c r="Y9" s="29"/>
       <c r="Z9" s="23"/>
       <c r="AA9" s="23"/>
       <c r="AB9" s="23"/>
-      <c r="AC9" s="43"/>
+      <c r="AC9" s="48"/>
       <c r="AD9" s="23"/>
       <c r="AE9" s="23"/>
       <c r="AF9" s="29"/>
@@ -4786,7 +4786,7 @@
       <c r="G10" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="43"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="28" t="s">
         <v>118</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>118</v>
       </c>
       <c r="N10" s="40"/>
-      <c r="O10" s="43"/>
+      <c r="O10" s="48"/>
       <c r="P10" s="23" t="s">
         <v>118</v>
       </c>
@@ -4820,14 +4820,14 @@
       <c r="U10" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V10" s="43"/>
+      <c r="V10" s="48"/>
       <c r="W10" s="23"/>
       <c r="X10" s="23"/>
       <c r="Y10" s="29"/>
       <c r="Z10" s="23"/>
       <c r="AA10" s="23"/>
       <c r="AB10" s="23"/>
-      <c r="AC10" s="43"/>
+      <c r="AC10" s="48"/>
       <c r="AD10" s="23"/>
       <c r="AE10" s="23"/>
       <c r="AF10" s="29"/>
@@ -4880,7 +4880,7 @@
       <c r="G11" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="43"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="28" t="s">
         <v>119</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>118</v>
       </c>
       <c r="N11" s="40"/>
-      <c r="O11" s="43"/>
+      <c r="O11" s="48"/>
       <c r="P11" s="23" t="s">
         <v>118</v>
       </c>
@@ -4914,14 +4914,14 @@
       <c r="U11" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V11" s="43"/>
+      <c r="V11" s="48"/>
       <c r="W11" s="23"/>
       <c r="X11" s="23"/>
       <c r="Y11" s="29"/>
       <c r="Z11" s="23"/>
       <c r="AA11" s="23"/>
       <c r="AB11" s="23"/>
-      <c r="AC11" s="43"/>
+      <c r="AC11" s="48"/>
       <c r="AD11" s="23"/>
       <c r="AE11" s="23"/>
       <c r="AF11" s="29"/>
@@ -4974,7 +4974,7 @@
       <c r="G12" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="43"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="28" t="s">
         <v>118</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>118</v>
       </c>
       <c r="N12" s="40"/>
-      <c r="O12" s="43"/>
+      <c r="O12" s="48"/>
       <c r="P12" s="23" t="s">
         <v>118</v>
       </c>
@@ -5008,14 +5008,14 @@
       <c r="U12" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V12" s="43"/>
+      <c r="V12" s="48"/>
       <c r="W12" s="23"/>
       <c r="X12" s="23"/>
       <c r="Y12" s="29"/>
       <c r="Z12" s="23"/>
       <c r="AA12" s="23"/>
       <c r="AB12" s="23"/>
-      <c r="AC12" s="43"/>
+      <c r="AC12" s="48"/>
       <c r="AD12" s="23"/>
       <c r="AE12" s="23"/>
       <c r="AF12" s="29"/>
@@ -5068,7 +5068,7 @@
       <c r="G13" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H13" s="43"/>
+      <c r="H13" s="48"/>
       <c r="I13" s="28" t="s">
         <v>118</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>118</v>
       </c>
       <c r="N13" s="40"/>
-      <c r="O13" s="43"/>
+      <c r="O13" s="48"/>
       <c r="P13" s="23" t="s">
         <v>118</v>
       </c>
@@ -5102,14 +5102,14 @@
       <c r="U13" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V13" s="43"/>
+      <c r="V13" s="48"/>
       <c r="W13" s="23"/>
       <c r="X13" s="23"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="23"/>
       <c r="AA13" s="23"/>
       <c r="AB13" s="23"/>
-      <c r="AC13" s="43"/>
+      <c r="AC13" s="48"/>
       <c r="AD13" s="23"/>
       <c r="AE13" s="23"/>
       <c r="AF13" s="29"/>
@@ -5151,7 +5151,7 @@
       <c r="G14" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="43"/>
+      <c r="H14" s="48"/>
       <c r="I14" s="28" t="s">
         <v>118</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>118</v>
       </c>
       <c r="N14" s="40"/>
-      <c r="O14" s="43"/>
+      <c r="O14" s="48"/>
       <c r="P14" s="23" t="s">
         <v>118</v>
       </c>
@@ -5185,14 +5185,14 @@
       <c r="U14" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V14" s="43"/>
+      <c r="V14" s="48"/>
       <c r="W14" s="23"/>
       <c r="X14" s="23"/>
       <c r="Y14" s="29"/>
       <c r="Z14" s="23"/>
       <c r="AA14" s="23"/>
       <c r="AB14" s="23"/>
-      <c r="AC14" s="43"/>
+      <c r="AC14" s="48"/>
       <c r="AD14" s="23"/>
       <c r="AE14" s="23"/>
       <c r="AF14" s="29"/>
@@ -5234,7 +5234,7 @@
       <c r="G15" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H15" s="43"/>
+      <c r="H15" s="48"/>
       <c r="I15" s="28" t="s">
         <v>118</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>118</v>
       </c>
       <c r="N15" s="40"/>
-      <c r="O15" s="43"/>
+      <c r="O15" s="48"/>
       <c r="P15" s="23" t="s">
         <v>118</v>
       </c>
@@ -5268,14 +5268,14 @@
       <c r="U15" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="V15" s="43"/>
+      <c r="V15" s="48"/>
       <c r="W15" s="23"/>
       <c r="X15" s="23"/>
       <c r="Y15" s="29"/>
       <c r="Z15" s="23"/>
       <c r="AA15" s="23"/>
       <c r="AB15" s="23"/>
-      <c r="AC15" s="43"/>
+      <c r="AC15" s="48"/>
       <c r="AD15" s="23"/>
       <c r="AE15" s="23"/>
       <c r="AF15" s="29"/>
@@ -5317,7 +5317,7 @@
       <c r="G16" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="43"/>
+      <c r="H16" s="48"/>
       <c r="I16" s="28" t="s">
         <v>118</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>118</v>
       </c>
       <c r="N16" s="40"/>
-      <c r="O16" s="43"/>
+      <c r="O16" s="48"/>
       <c r="P16" s="23" t="s">
         <v>118</v>
       </c>
@@ -5351,14 +5351,14 @@
       <c r="U16" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V16" s="43"/>
+      <c r="V16" s="48"/>
       <c r="W16" s="23"/>
       <c r="X16" s="23"/>
       <c r="Y16" s="29"/>
       <c r="Z16" s="23"/>
       <c r="AA16" s="23"/>
       <c r="AB16" s="23"/>
-      <c r="AC16" s="43"/>
+      <c r="AC16" s="48"/>
       <c r="AD16" s="23"/>
       <c r="AE16" s="23"/>
       <c r="AF16" s="29"/>
@@ -5402,7 +5402,7 @@
       <c r="G17" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H17" s="43"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="28" t="s">
         <v>118</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>119</v>
       </c>
       <c r="N17" s="40"/>
-      <c r="O17" s="43"/>
+      <c r="O17" s="48"/>
       <c r="P17" s="23" t="s">
         <v>119</v>
       </c>
@@ -5436,14 +5436,14 @@
       <c r="U17" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="V17" s="43"/>
+      <c r="V17" s="48"/>
       <c r="W17" s="23"/>
       <c r="X17" s="23"/>
       <c r="Y17" s="29"/>
       <c r="Z17" s="23"/>
       <c r="AA17" s="23"/>
       <c r="AB17" s="23"/>
-      <c r="AC17" s="43"/>
+      <c r="AC17" s="48"/>
       <c r="AD17" s="23"/>
       <c r="AE17" s="23"/>
       <c r="AF17" s="29"/>
@@ -5493,7 +5493,7 @@
       <c r="G18" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H18" s="43"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="28" t="s">
         <v>118</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>118</v>
       </c>
       <c r="N18" s="40"/>
-      <c r="O18" s="43"/>
+      <c r="O18" s="48"/>
       <c r="P18" s="23" t="s">
         <v>118</v>
       </c>
@@ -5527,14 +5527,14 @@
       <c r="U18" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V18" s="43"/>
+      <c r="V18" s="48"/>
       <c r="W18" s="23"/>
       <c r="X18" s="23"/>
       <c r="Y18" s="29"/>
       <c r="Z18" s="23"/>
       <c r="AA18" s="23"/>
       <c r="AB18" s="23"/>
-      <c r="AC18" s="43"/>
+      <c r="AC18" s="48"/>
       <c r="AD18" s="23"/>
       <c r="AE18" s="23"/>
       <c r="AF18" s="29"/>
@@ -5587,7 +5587,7 @@
       <c r="G19" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H19" s="43"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="28" t="s">
         <v>118</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>118</v>
       </c>
       <c r="N19" s="40"/>
-      <c r="O19" s="43"/>
+      <c r="O19" s="48"/>
       <c r="P19" s="23" t="s">
         <v>118</v>
       </c>
@@ -5621,14 +5621,14 @@
       <c r="U19" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="V19" s="43"/>
+      <c r="V19" s="48"/>
       <c r="W19" s="23"/>
       <c r="X19" s="23"/>
       <c r="Y19" s="29"/>
       <c r="Z19" s="23"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="23"/>
-      <c r="AC19" s="43"/>
+      <c r="AC19" s="48"/>
       <c r="AD19" s="23"/>
       <c r="AE19" s="23"/>
       <c r="AF19" s="29"/>
@@ -5681,7 +5681,7 @@
       <c r="G20" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="43"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="28" t="s">
         <v>118</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>118</v>
       </c>
       <c r="N20" s="40"/>
-      <c r="O20" s="43"/>
+      <c r="O20" s="48"/>
       <c r="P20" s="23" t="s">
         <v>118</v>
       </c>
@@ -5715,14 +5715,14 @@
       <c r="U20" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V20" s="43"/>
+      <c r="V20" s="48"/>
       <c r="W20" s="23"/>
       <c r="X20" s="23"/>
       <c r="Y20" s="29"/>
       <c r="Z20" s="23"/>
       <c r="AA20" s="23"/>
       <c r="AB20" s="23"/>
-      <c r="AC20" s="43"/>
+      <c r="AC20" s="48"/>
       <c r="AD20" s="23"/>
       <c r="AE20" s="23"/>
       <c r="AF20" s="29"/>
@@ -5775,7 +5775,7 @@
       <c r="G21" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H21" s="43"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="28" t="s">
         <v>118</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>118</v>
       </c>
       <c r="N21" s="40"/>
-      <c r="O21" s="43"/>
+      <c r="O21" s="48"/>
       <c r="P21" s="23" t="s">
         <v>118</v>
       </c>
@@ -5809,14 +5809,14 @@
       <c r="U21" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V21" s="43"/>
+      <c r="V21" s="48"/>
       <c r="W21" s="23"/>
       <c r="X21" s="23"/>
       <c r="Y21" s="29"/>
       <c r="Z21" s="23"/>
       <c r="AA21" s="23"/>
       <c r="AB21" s="23"/>
-      <c r="AC21" s="43"/>
+      <c r="AC21" s="48"/>
       <c r="AD21" s="23"/>
       <c r="AE21" s="23"/>
       <c r="AF21" s="29"/>
@@ -5858,7 +5858,7 @@
       <c r="G22" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H22" s="43"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="28" t="s">
         <v>118</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>118</v>
       </c>
       <c r="N22" s="40"/>
-      <c r="O22" s="43"/>
+      <c r="O22" s="48"/>
       <c r="P22" s="23" t="s">
         <v>118</v>
       </c>
@@ -5892,14 +5892,14 @@
       <c r="U22" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V22" s="43"/>
+      <c r="V22" s="48"/>
       <c r="W22" s="23"/>
       <c r="X22" s="23"/>
       <c r="Y22" s="29"/>
       <c r="Z22" s="23"/>
       <c r="AA22" s="23"/>
       <c r="AB22" s="23"/>
-      <c r="AC22" s="43"/>
+      <c r="AC22" s="48"/>
       <c r="AD22" s="23"/>
       <c r="AE22" s="23"/>
       <c r="AF22" s="29"/>
@@ -5941,7 +5941,7 @@
       <c r="G23" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H23" s="43"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="28" t="s">
         <v>119</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>118</v>
       </c>
       <c r="N23" s="40"/>
-      <c r="O23" s="43"/>
+      <c r="O23" s="48"/>
       <c r="P23" s="23" t="s">
         <v>118</v>
       </c>
@@ -5975,14 +5975,14 @@
       <c r="U23" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V23" s="43"/>
+      <c r="V23" s="48"/>
       <c r="W23" s="23"/>
       <c r="X23" s="23"/>
       <c r="Y23" s="29"/>
       <c r="Z23" s="23"/>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
-      <c r="AC23" s="43"/>
+      <c r="AC23" s="48"/>
       <c r="AD23" s="23"/>
       <c r="AE23" s="23"/>
       <c r="AF23" s="29"/>
@@ -6024,7 +6024,7 @@
       <c r="G24" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H24" s="43"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="28" t="s">
         <v>118</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>118</v>
       </c>
       <c r="N24" s="40"/>
-      <c r="O24" s="43"/>
+      <c r="O24" s="48"/>
       <c r="P24" s="23" t="s">
         <v>118</v>
       </c>
@@ -6058,14 +6058,14 @@
       <c r="U24" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V24" s="43"/>
+      <c r="V24" s="48"/>
       <c r="W24" s="23"/>
       <c r="X24" s="23"/>
       <c r="Y24" s="29"/>
       <c r="Z24" s="23"/>
       <c r="AA24" s="23"/>
       <c r="AB24" s="23"/>
-      <c r="AC24" s="43"/>
+      <c r="AC24" s="48"/>
       <c r="AD24" s="23"/>
       <c r="AE24" s="23"/>
       <c r="AF24" s="29"/>
@@ -6107,7 +6107,7 @@
       <c r="G25" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H25" s="43"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="28" t="s">
         <v>119</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>119</v>
       </c>
       <c r="N25" s="40"/>
-      <c r="O25" s="43"/>
+      <c r="O25" s="48"/>
       <c r="P25" s="23" t="s">
         <v>118</v>
       </c>
@@ -6141,14 +6141,14 @@
       <c r="U25" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V25" s="43"/>
+      <c r="V25" s="48"/>
       <c r="W25" s="23"/>
       <c r="X25" s="23"/>
       <c r="Y25" s="29"/>
       <c r="Z25" s="23"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="23"/>
-      <c r="AC25" s="43"/>
+      <c r="AC25" s="48"/>
       <c r="AD25" s="23"/>
       <c r="AE25" s="23"/>
       <c r="AF25" s="29"/>
@@ -6190,7 +6190,7 @@
       <c r="G26" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="43"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="28" t="s">
         <v>119</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>119</v>
       </c>
       <c r="N26" s="40"/>
-      <c r="O26" s="43"/>
+      <c r="O26" s="48"/>
       <c r="P26" s="23" t="s">
         <v>118</v>
       </c>
@@ -6224,14 +6224,14 @@
       <c r="U26" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V26" s="43"/>
+      <c r="V26" s="48"/>
       <c r="W26" s="23"/>
       <c r="X26" s="23"/>
       <c r="Y26" s="29"/>
       <c r="Z26" s="23"/>
       <c r="AA26" s="23"/>
       <c r="AB26" s="23"/>
-      <c r="AC26" s="43"/>
+      <c r="AC26" s="48"/>
       <c r="AD26" s="23"/>
       <c r="AE26" s="23"/>
       <c r="AF26" s="29"/>
@@ -6273,7 +6273,7 @@
       <c r="G27" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H27" s="43"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="28" t="s">
         <v>118</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>119</v>
       </c>
       <c r="N27" s="40"/>
-      <c r="O27" s="43"/>
+      <c r="O27" s="48"/>
       <c r="P27" s="23" t="s">
         <v>118</v>
       </c>
@@ -6307,14 +6307,14 @@
       <c r="U27" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="V27" s="43"/>
+      <c r="V27" s="48"/>
       <c r="W27" s="23"/>
       <c r="X27" s="23"/>
       <c r="Y27" s="29"/>
       <c r="Z27" s="23"/>
       <c r="AA27" s="23"/>
       <c r="AB27" s="23"/>
-      <c r="AC27" s="43"/>
+      <c r="AC27" s="48"/>
       <c r="AD27" s="23"/>
       <c r="AE27" s="23"/>
       <c r="AF27" s="29"/>
@@ -6356,7 +6356,7 @@
       <c r="G28" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H28" s="43"/>
+      <c r="H28" s="48"/>
       <c r="I28" s="28" t="s">
         <v>118</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>119</v>
       </c>
       <c r="N28" s="40"/>
-      <c r="O28" s="43"/>
+      <c r="O28" s="48"/>
       <c r="P28" s="23" t="s">
         <v>118</v>
       </c>
@@ -6390,14 +6390,14 @@
       <c r="U28" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="V28" s="43"/>
+      <c r="V28" s="48"/>
       <c r="W28" s="23"/>
       <c r="X28" s="23"/>
       <c r="Y28" s="29"/>
       <c r="Z28" s="23"/>
       <c r="AA28" s="23"/>
       <c r="AB28" s="23"/>
-      <c r="AC28" s="43"/>
+      <c r="AC28" s="48"/>
       <c r="AD28" s="23"/>
       <c r="AE28" s="23"/>
       <c r="AF28" s="29"/>
@@ -6439,7 +6439,7 @@
       <c r="G29" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H29" s="43"/>
+      <c r="H29" s="48"/>
       <c r="I29" s="28" t="s">
         <v>118</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>118</v>
       </c>
       <c r="N29" s="40"/>
-      <c r="O29" s="43"/>
+      <c r="O29" s="48"/>
       <c r="P29" s="23" t="s">
         <v>119</v>
       </c>
@@ -6473,14 +6473,14 @@
       <c r="U29" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V29" s="43"/>
+      <c r="V29" s="48"/>
       <c r="W29" s="23"/>
       <c r="X29" s="23"/>
       <c r="Y29" s="29"/>
       <c r="Z29" s="23"/>
       <c r="AA29" s="23"/>
       <c r="AB29" s="23"/>
-      <c r="AC29" s="43"/>
+      <c r="AC29" s="48"/>
       <c r="AD29" s="23"/>
       <c r="AE29" s="23"/>
       <c r="AF29" s="29"/>
@@ -6501,7 +6501,7 @@
       <c r="AO29" s="15"/>
     </row>
     <row r="30" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="10">
         <v>26</v>
       </c>
       <c r="B30" s="10"/>
@@ -6520,7 +6520,7 @@
       <c r="G30" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H30" s="43"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="28" t="s">
         <v>119</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>118</v>
       </c>
       <c r="N30" s="40"/>
-      <c r="O30" s="43"/>
+      <c r="O30" s="48"/>
       <c r="P30" s="23" t="s">
         <v>118</v>
       </c>
@@ -6554,14 +6554,14 @@
       <c r="U30" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V30" s="43"/>
+      <c r="V30" s="48"/>
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
       <c r="Y30" s="29"/>
       <c r="Z30" s="23"/>
       <c r="AA30" s="23"/>
       <c r="AB30" s="23"/>
-      <c r="AC30" s="43"/>
+      <c r="AC30" s="48"/>
       <c r="AD30" s="23"/>
       <c r="AE30" s="23"/>
       <c r="AF30" s="29"/>
@@ -6582,7 +6582,7 @@
       <c r="AO30" s="15"/>
     </row>
     <row r="31" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="5">
         <v>27</v>
       </c>
       <c r="B31" s="10"/>
@@ -6601,7 +6601,7 @@
       <c r="G31" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H31" s="43"/>
+      <c r="H31" s="48"/>
       <c r="I31" s="28" t="s">
         <v>118</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>118</v>
       </c>
       <c r="N31" s="40"/>
-      <c r="O31" s="43"/>
+      <c r="O31" s="48"/>
       <c r="P31" s="23" t="s">
         <v>118</v>
       </c>
@@ -6635,14 +6635,14 @@
       <c r="U31" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V31" s="43"/>
+      <c r="V31" s="48"/>
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
       <c r="Y31" s="29"/>
       <c r="Z31" s="23"/>
       <c r="AA31" s="23"/>
       <c r="AB31" s="23"/>
-      <c r="AC31" s="43"/>
+      <c r="AC31" s="48"/>
       <c r="AD31" s="23"/>
       <c r="AE31" s="23"/>
       <c r="AF31" s="29"/>
@@ -6663,7 +6663,7 @@
       <c r="AO31" s="15"/>
     </row>
     <row r="32" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="10">
         <v>28</v>
       </c>
       <c r="B32" s="10"/>
@@ -6682,7 +6682,7 @@
       <c r="G32" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H32" s="43"/>
+      <c r="H32" s="48"/>
       <c r="I32" s="28" t="s">
         <v>118</v>
       </c>
@@ -6699,7 +6699,7 @@
         <v>118</v>
       </c>
       <c r="N32" s="40"/>
-      <c r="O32" s="43"/>
+      <c r="O32" s="48"/>
       <c r="P32" s="23" t="s">
         <v>119</v>
       </c>
@@ -6716,14 +6716,14 @@
       <c r="U32" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V32" s="43"/>
+      <c r="V32" s="48"/>
       <c r="W32" s="23"/>
       <c r="X32" s="23"/>
       <c r="Y32" s="29"/>
       <c r="Z32" s="23"/>
       <c r="AA32" s="23"/>
       <c r="AB32" s="23"/>
-      <c r="AC32" s="43"/>
+      <c r="AC32" s="48"/>
       <c r="AD32" s="23"/>
       <c r="AE32" s="23"/>
       <c r="AF32" s="29"/>
@@ -6765,7 +6765,7 @@
       <c r="G33" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="H33" s="43"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="28" t="s">
         <v>118</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>118</v>
       </c>
       <c r="N33" s="40"/>
-      <c r="O33" s="43"/>
+      <c r="O33" s="48"/>
       <c r="P33" s="23" t="s">
         <v>118</v>
       </c>
@@ -6799,14 +6799,14 @@
       <c r="U33" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V33" s="43"/>
+      <c r="V33" s="48"/>
       <c r="W33" s="23"/>
       <c r="X33" s="23"/>
       <c r="Y33" s="29"/>
       <c r="Z33" s="23"/>
       <c r="AA33" s="23"/>
       <c r="AB33" s="23"/>
-      <c r="AC33" s="43"/>
+      <c r="AC33" s="48"/>
       <c r="AD33" s="23"/>
       <c r="AE33" s="23"/>
       <c r="AF33" s="29"/>
@@ -6848,7 +6848,7 @@
       <c r="G34" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H34" s="43"/>
+      <c r="H34" s="48"/>
       <c r="I34" s="28" t="s">
         <v>118</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>119</v>
       </c>
       <c r="N34" s="40"/>
-      <c r="O34" s="43"/>
+      <c r="O34" s="48"/>
       <c r="P34" s="23" t="s">
         <v>118</v>
       </c>
@@ -6882,14 +6882,14 @@
       <c r="U34" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V34" s="43"/>
+      <c r="V34" s="48"/>
       <c r="W34" s="23"/>
       <c r="X34" s="23"/>
       <c r="Y34" s="29"/>
       <c r="Z34" s="23"/>
       <c r="AA34" s="23"/>
       <c r="AB34" s="23"/>
-      <c r="AC34" s="43"/>
+      <c r="AC34" s="48"/>
       <c r="AD34" s="23"/>
       <c r="AE34" s="23"/>
       <c r="AF34" s="29"/>
@@ -6929,7 +6929,7 @@
       <c r="G35" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="H35" s="44"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="28" t="s">
         <v>118</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>118</v>
       </c>
       <c r="N35" s="41"/>
-      <c r="O35" s="44"/>
+      <c r="O35" s="49"/>
       <c r="P35" s="23" t="s">
         <v>118</v>
       </c>
@@ -6963,14 +6963,14 @@
       <c r="U35" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="V35" s="44"/>
+      <c r="V35" s="49"/>
       <c r="W35" s="23"/>
       <c r="X35" s="23"/>
       <c r="Y35" s="29"/>
       <c r="Z35" s="23"/>
       <c r="AA35" s="23"/>
       <c r="AB35" s="23"/>
-      <c r="AC35" s="44"/>
+      <c r="AC35" s="49"/>
       <c r="AD35" s="23"/>
       <c r="AE35" s="23"/>
       <c r="AF35" s="29"/>
@@ -6992,6 +6992,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H35"/>
+    <mergeCell ref="N5:N35"/>
+    <mergeCell ref="O5:O35"/>
+    <mergeCell ref="V5:V35"/>
+    <mergeCell ref="AC5:AC35"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AM3"/>
@@ -7002,13 +7009,6 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="H5:H35"/>
-    <mergeCell ref="N5:N35"/>
-    <mergeCell ref="O5:O35"/>
-    <mergeCell ref="V5:V35"/>
-    <mergeCell ref="AC5:AC35"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B33">
     <cfRule type="duplicateValues" dxfId="12" priority="301"/>
